--- a/บันทึกผลการดำเนินงาน_RM_2569.xlsx
+++ b/บันทึกผลการดำเนินงาน_RM_2569.xlsx
@@ -1277,12 +1277,14 @@
       <c r="AA2" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB2" s="14" t="n"/>
+      <c r="AB2" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC2" s="14" t="n"/>
       <c r="AD2" s="14" t="n"/>
       <c r="AE2" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ การปรับปรุงโครงสร้าง เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ การปรับปรุงโครงสร้าง เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF2" s="15" t="n"/>
@@ -1385,12 +1387,14 @@
       <c r="AA3" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB3" s="14" t="n"/>
+      <c r="AB3" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC3" s="14" t="n"/>
       <c r="AD3" s="14" t="n"/>
       <c r="AE3" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ โครงสร้างหน่วยงานที่ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ โครงสร้างหน่วยงานที่ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF3" s="15" t="n"/>
@@ -1493,12 +1497,14 @@
       <c r="AA4" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB4" s="14" t="n"/>
+      <c r="AB4" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC4" s="14" t="n"/>
       <c r="AD4" s="14" t="n"/>
       <c r="AE4" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ การจัดทำ Risk Taxono เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ การจัดทำ Risk Taxono เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF4" s="15" t="n"/>
@@ -1589,12 +1595,14 @@
       <c r="AA5" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB5" s="14" t="n"/>
+      <c r="AB5" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC5" s="14" t="n"/>
       <c r="AD5" s="14" t="n"/>
       <c r="AE5" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ การวิเคราะห์ตัวชี้วั เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ การวิเคราะห์ตัวชี้วั เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF5" s="15" t="n"/>
@@ -1673,12 +1681,14 @@
       <c r="AA6" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="AB6" s="14" t="n"/>
+      <c r="AB6" s="14" t="n">
+        <v>80</v>
+      </c>
       <c r="AC6" s="14" t="n"/>
       <c r="AD6" s="14" t="n"/>
       <c r="AE6" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ การสร้างวัฒนธรรม GRC เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ การสร้างวัฒนธรรม GRC เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF6" s="15" t="n"/>
@@ -1745,10 +1755,16 @@
       <c r="Y7" s="14" t="n"/>
       <c r="Z7" s="14" t="n"/>
       <c r="AA7" s="14" t="n"/>
-      <c r="AB7" s="14" t="n"/>
+      <c r="AB7" s="14" t="n">
+        <v>33.3</v>
+      </c>
       <c r="AC7" s="14" t="n"/>
       <c r="AD7" s="14" t="n"/>
-      <c r="AE7" s="15" t="n"/>
+      <c r="AE7" s="15" t="inlineStr">
+        <is>
+          <t>ดำเนินการ การพัฒนากระบวนการจัด เป็นไปตามแผน (ถึง ต.ค.)</t>
+        </is>
+      </c>
       <c r="AF7" s="15" t="n"/>
       <c r="AG7" s="16" t="inlineStr">
         <is>
@@ -1813,10 +1829,16 @@
       <c r="Y8" s="14" t="n"/>
       <c r="Z8" s="14" t="n"/>
       <c r="AA8" s="14" t="n"/>
-      <c r="AB8" s="14" t="n"/>
+      <c r="AB8" s="14" t="n">
+        <v>33.3</v>
+      </c>
       <c r="AC8" s="14" t="n"/>
       <c r="AD8" s="14" t="n"/>
-      <c r="AE8" s="15" t="n"/>
+      <c r="AE8" s="15" t="inlineStr">
+        <is>
+          <t>ดำเนินการ การเชื่อมโยงการปฏิบั เป็นไปตามแผน (ถึง ต.ค.)</t>
+        </is>
+      </c>
       <c r="AF8" s="15" t="n"/>
       <c r="AG8" s="16" t="inlineStr">
         <is>
@@ -1881,10 +1903,16 @@
       <c r="Y9" s="14" t="n"/>
       <c r="Z9" s="14" t="n"/>
       <c r="AA9" s="14" t="n"/>
-      <c r="AB9" s="14" t="n"/>
+      <c r="AB9" s="14" t="n">
+        <v>33.3</v>
+      </c>
       <c r="AC9" s="14" t="n"/>
       <c r="AD9" s="14" t="n"/>
-      <c r="AE9" s="15" t="n"/>
+      <c r="AE9" s="15" t="inlineStr">
+        <is>
+          <t>ดำเนินการ การปรับปรุงนโยบายการ เป็นไปตามแผน (ถึง ต.ค.)</t>
+        </is>
+      </c>
       <c r="AF9" s="15" t="n"/>
       <c r="AG9" s="16" t="inlineStr">
         <is>
@@ -1985,12 +2013,14 @@
       <c r="AA10" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB10" s="14" t="n"/>
+      <c r="AB10" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC10" s="14" t="n"/>
       <c r="AD10" s="14" t="n"/>
       <c r="AE10" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ การผลักดันให้มีหน่วย เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ การผลักดันให้มีหน่วย เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF10" s="15" t="n"/>
@@ -2081,12 +2111,14 @@
       <c r="AA11" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB11" s="14" t="n"/>
+      <c r="AB11" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC11" s="14" t="n"/>
       <c r="AD11" s="14" t="n"/>
       <c r="AE11" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ การบูรณาการข้อมูลกระ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ การบูรณาการข้อมูลกระ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF11" s="15" t="n"/>
@@ -2165,12 +2197,14 @@
       <c r="AA12" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB12" s="14" t="n"/>
+      <c r="AB12" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC12" s="14" t="n"/>
       <c r="AD12" s="14" t="n"/>
       <c r="AE12" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ การปรับแนวทางการประเ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ การปรับแนวทางการประเ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF12" s="15" t="n"/>
@@ -2273,12 +2307,14 @@
       <c r="AA13" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB13" s="14" t="n"/>
+      <c r="AB13" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC13" s="14" t="n"/>
       <c r="AD13" s="14" t="n"/>
       <c r="AE13" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ การจัดทำแนวทาง/เอกสา เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ การจัดทำแนวทาง/เอกสา เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF13" s="15" t="n"/>
@@ -2381,12 +2417,14 @@
       <c r="AA14" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB14" s="14" t="n"/>
+      <c r="AB14" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC14" s="14" t="n"/>
       <c r="AD14" s="14" t="n"/>
       <c r="AE14" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ การพัฒนาเครื่องมือติ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ การพัฒนาเครื่องมือติ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF14" s="15" t="n"/>
@@ -2489,12 +2527,14 @@
       <c r="AA15" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB15" s="14" t="n"/>
+      <c r="AB15" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC15" s="14" t="n"/>
       <c r="AD15" s="14" t="n"/>
       <c r="AE15" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ การพัฒนาทะเบียนกฎหมา เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ การพัฒนาทะเบียนกฎหมา เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF15" s="15" t="n"/>
@@ -2577,12 +2617,14 @@
       <c r="AA16" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="AB16" s="14" t="n"/>
+      <c r="AB16" s="14" t="n">
+        <v>50</v>
+      </c>
       <c r="AC16" s="14" t="n"/>
       <c r="AD16" s="14" t="n"/>
       <c r="AE16" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ทบทวนนโยบาย GRC เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ทบทวนนโยบาย GRC เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF16" s="15" t="n"/>
@@ -2673,12 +2715,14 @@
       <c r="AA17" s="14" t="n">
         <v>62.5</v>
       </c>
-      <c r="AB17" s="14" t="n"/>
+      <c r="AB17" s="14" t="n">
+        <v>75</v>
+      </c>
       <c r="AC17" s="14" t="n"/>
       <c r="AD17" s="14" t="n"/>
       <c r="AE17" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ทบทวนโครงสร้างและบทบ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ทบทวนโครงสร้างและบทบ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF17" s="15" t="n"/>
@@ -2765,12 +2809,14 @@
       <c r="AA18" s="14" t="n">
         <v>62.5</v>
       </c>
-      <c r="AB18" s="14" t="n"/>
+      <c r="AB18" s="14" t="n">
+        <v>75</v>
+      </c>
       <c r="AC18" s="14" t="n"/>
       <c r="AD18" s="14" t="n"/>
       <c r="AE18" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ทบทวนกรอบการดำเนินงา เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ทบทวนกรอบการดำเนินงา เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF18" s="15" t="n"/>
@@ -2877,12 +2923,14 @@
       <c r="AA19" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB19" s="14" t="n"/>
+      <c r="AB19" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC19" s="14" t="n"/>
       <c r="AD19" s="14" t="n"/>
       <c r="AE19" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ทบทวน Competency / พ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ทบทวน Competency / พ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF19" s="15" t="n"/>
@@ -2989,12 +3037,14 @@
       <c r="AA20" s="14" t="n">
         <v>61.5</v>
       </c>
-      <c r="AB20" s="14" t="n"/>
+      <c r="AB20" s="14" t="n">
+        <v>76.90000000000001</v>
+      </c>
       <c r="AC20" s="14" t="n"/>
       <c r="AD20" s="14" t="n"/>
       <c r="AE20" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ อบรมและพัฒนาพนักงานต เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ อบรมและพัฒนาพนักงานต เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF20" s="15" t="n"/>
@@ -3101,12 +3151,14 @@
       <c r="AA21" s="14" t="n">
         <v>83.3</v>
       </c>
-      <c r="AB21" s="14" t="n"/>
+      <c r="AB21" s="14" t="n">
+        <v>88.90000000000001</v>
+      </c>
       <c r="AC21" s="14" t="n"/>
       <c r="AD21" s="14" t="n"/>
       <c r="AE21" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ สื่อสารสร้างความตระห เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ สื่อสารสร้างความตระห เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF21" s="15" t="n"/>
@@ -3189,12 +3241,14 @@
       <c r="AA22" s="14" t="n">
         <v>57.1</v>
       </c>
-      <c r="AB22" s="14" t="n"/>
+      <c r="AB22" s="14" t="n">
+        <v>71.40000000000001</v>
+      </c>
       <c r="AC22" s="14" t="n"/>
       <c r="AD22" s="14" t="n"/>
       <c r="AE22" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ สำรวจความตระหนักและท เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ สำรวจความตระหนักและท เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF22" s="15" t="n"/>
@@ -3301,12 +3355,14 @@
       <c r="AA23" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB23" s="14" t="n"/>
+      <c r="AB23" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC23" s="14" t="n"/>
       <c r="AD23" s="14" t="n"/>
       <c r="AE23" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ทบทวนการจัดทำการเชื่ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ทบทวนการจัดทำการเชื่ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF23" s="15" t="n"/>
@@ -3413,12 +3469,14 @@
       <c r="AA24" s="14" t="n">
         <v>64.7</v>
       </c>
-      <c r="AB24" s="14" t="n"/>
+      <c r="AB24" s="14" t="n">
+        <v>76.5</v>
+      </c>
       <c r="AC24" s="14" t="n"/>
       <c r="AD24" s="14" t="n"/>
       <c r="AE24" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ดำเนินการตามโครงการ  เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ดำเนินการตามโครงการ  เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF24" s="15" t="n"/>
@@ -3525,12 +3583,14 @@
       <c r="AA25" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB25" s="14" t="n"/>
+      <c r="AB25" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC25" s="14" t="n"/>
       <c r="AD25" s="14" t="n"/>
       <c r="AE25" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ทบทวนหลักการกำหนด RA เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ทบทวนหลักการกำหนด RA เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF25" s="15" t="inlineStr">
@@ -3641,12 +3701,14 @@
       <c r="AA26" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="AB26" s="14" t="n"/>
+      <c r="AB26" s="14" t="n">
+        <v>86.7</v>
+      </c>
       <c r="AC26" s="14" t="n"/>
       <c r="AD26" s="14" t="n"/>
       <c r="AE26" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ระบุ Emerging Risk เ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ระบุ Emerging Risk เ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF26" s="15" t="n"/>
@@ -3741,12 +3803,14 @@
       <c r="AA27" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB27" s="14" t="n"/>
+      <c r="AB27" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC27" s="14" t="n"/>
       <c r="AD27" s="14" t="n"/>
       <c r="AE27" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ระบุ Intelligent Ris เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ระบุ Intelligent Ris เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF27" s="15" t="n"/>
@@ -3841,12 +3905,14 @@
       <c r="AA28" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB28" s="14" t="n"/>
+      <c r="AB28" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC28" s="14" t="n"/>
       <c r="AD28" s="14" t="n"/>
       <c r="AE28" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ระบุและวิเคราะห์ความ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ระบุและวิเคราะห์ความ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF28" s="15" t="n"/>
@@ -3937,12 +4003,14 @@
       <c r="AA29" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB29" s="14" t="n"/>
+      <c r="AB29" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC29" s="14" t="n"/>
       <c r="AD29" s="14" t="n"/>
       <c r="AE29" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ทบทวนแบบฟอร์มและเกณฑ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ทบทวนแบบฟอร์มและเกณฑ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF29" s="15" t="n"/>
@@ -4029,12 +4097,14 @@
       <c r="AA30" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB30" s="14" t="n"/>
+      <c r="AB30" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC30" s="14" t="n"/>
       <c r="AD30" s="14" t="n"/>
       <c r="AE30" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ สื่อสารแบบฟอร์มการปร เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ สื่อสารแบบฟอร์มการปร เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF30" s="15" t="n"/>
@@ -4121,12 +4191,14 @@
       <c r="AA31" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB31" s="14" t="n"/>
+      <c r="AB31" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC31" s="14" t="n"/>
       <c r="AD31" s="14" t="n"/>
       <c r="AE31" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ติดตามการวิเคราะห์ ร เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ติดตามการวิเคราะห์ ร เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF31" s="15" t="inlineStr">
@@ -4237,12 +4309,14 @@
       <c r="AA32" s="14" t="n">
         <v>73.7</v>
       </c>
-      <c r="AB32" s="14" t="n"/>
+      <c r="AB32" s="14" t="n">
+        <v>78.90000000000001</v>
+      </c>
       <c r="AC32" s="14" t="n"/>
       <c r="AD32" s="14" t="n"/>
       <c r="AE32" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ รวบรวม/วิเคราะห์ข้อม เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ รวบรวม/วิเคราะห์ข้อม เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF32" s="15" t="n"/>
@@ -4329,12 +4403,14 @@
       <c r="AA33" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="AB33" s="14" t="n"/>
+      <c r="AB33" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC33" s="14" t="n"/>
       <c r="AD33" s="14" t="n"/>
       <c r="AE33" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ คัดเลือกปัจจัยเสี่ยง เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ คัดเลือกปัจจัยเสี่ยง เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF33" s="15" t="n"/>
@@ -4417,12 +4493,14 @@
       <c r="AA34" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="AB34" s="14" t="n"/>
+      <c r="AB34" s="14" t="n">
+        <v>100</v>
+      </c>
       <c r="AC34" s="14" t="n"/>
       <c r="AD34" s="14" t="n"/>
       <c r="AE34" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ จัดให้มีการประเมินคว เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ จัดให้มีการประเมินคว เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF34" s="15" t="n"/>
@@ -4501,12 +4579,14 @@
       <c r="AA35" s="14" t="n">
         <v>42.9</v>
       </c>
-      <c r="AB35" s="14" t="n"/>
+      <c r="AB35" s="14" t="n">
+        <v>71.40000000000001</v>
+      </c>
       <c r="AC35" s="14" t="n"/>
       <c r="AD35" s="14" t="n"/>
       <c r="AE35" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ พิจารณาและคัดเลือกวิ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ พิจารณาและคัดเลือกวิ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF35" s="15" t="n"/>
@@ -4585,12 +4665,14 @@
       <c r="AA36" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="AB36" s="14" t="n"/>
+      <c r="AB36" s="14" t="n">
+        <v>75</v>
+      </c>
       <c r="AC36" s="14" t="n"/>
       <c r="AD36" s="14" t="n"/>
       <c r="AE36" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ จัดทำแผนบริหารความเส เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ จัดทำแผนบริหารความเส เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF36" s="15" t="n"/>
@@ -4697,12 +4779,14 @@
       <c r="AA37" s="14" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="AB37" s="14" t="n"/>
+      <c r="AB37" s="14" t="n">
+        <v>82.09999999999999</v>
+      </c>
       <c r="AC37" s="14" t="n"/>
       <c r="AD37" s="14" t="n"/>
       <c r="AE37" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ติดตามและรายงานผลการ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ติดตามและรายงานผลการ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF37" s="15" t="n"/>
@@ -4809,12 +4893,14 @@
       <c r="AA38" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB38" s="14" t="n"/>
+      <c r="AB38" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC38" s="14" t="n"/>
       <c r="AD38" s="14" t="n"/>
       <c r="AE38" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ พัฒนาระบบเทคโนโลยีดิ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ พัฒนาระบบเทคโนโลยีดิ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF38" s="15" t="n"/>
@@ -4885,10 +4971,16 @@
       <c r="Y39" s="14" t="n"/>
       <c r="Z39" s="14" t="n"/>
       <c r="AA39" s="14" t="n"/>
-      <c r="AB39" s="14" t="n"/>
+      <c r="AB39" s="14" t="n">
+        <v>42.9</v>
+      </c>
       <c r="AC39" s="14" t="n"/>
       <c r="AD39" s="14" t="n"/>
-      <c r="AE39" s="15" t="n"/>
+      <c r="AE39" s="15" t="inlineStr">
+        <is>
+          <t>ดำเนินการ ทบทวน ประเมินประสิทธ เป็นไปตามแผน (ถึง ต.ค.)</t>
+        </is>
+      </c>
       <c r="AF39" s="15" t="n"/>
       <c r="AG39" s="16" t="inlineStr">
         <is>
@@ -4993,12 +5085,14 @@
       <c r="AA40" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="AB40" s="14" t="n"/>
+      <c r="AB40" s="14" t="n">
+        <v>86.7</v>
+      </c>
       <c r="AC40" s="14" t="n"/>
       <c r="AD40" s="14" t="n"/>
       <c r="AE40" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ วิเคราะห์ผลกระทบทางธ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ วิเคราะห์ผลกระทบทางธ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF40" s="15" t="n"/>
@@ -5097,12 +5191,14 @@
       <c r="AA41" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="AB41" s="14" t="n"/>
+      <c r="AB41" s="14" t="n">
+        <v>80</v>
+      </c>
       <c r="AC41" s="14" t="n"/>
       <c r="AD41" s="14" t="n"/>
       <c r="AE41" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ติดตามและเข้าร่วมฝึก เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ติดตามและเข้าร่วมฝึก เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF41" s="15" t="n"/>
@@ -5201,12 +5297,14 @@
       <c r="AA42" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB42" s="14" t="n"/>
+      <c r="AB42" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC42" s="14" t="n"/>
       <c r="AD42" s="14" t="n"/>
       <c r="AE42" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ฝึกซ้อมสถานการณ์ใหญ่ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ฝึกซ้อมสถานการณ์ใหญ่ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF42" s="15" t="n"/>
@@ -5313,12 +5411,14 @@
       <c r="AA43" s="14" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="AB43" s="14" t="n"/>
+      <c r="AB43" s="14" t="n">
+        <v>90.3</v>
+      </c>
       <c r="AC43" s="14" t="n"/>
       <c r="AD43" s="14" t="n"/>
       <c r="AE43" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ สร้างความตระหนักและส เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ สร้างความตระหนักและส เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF43" s="15" t="n"/>
@@ -5389,10 +5489,16 @@
       <c r="Y44" s="14" t="n"/>
       <c r="Z44" s="14" t="n"/>
       <c r="AA44" s="14" t="n"/>
-      <c r="AB44" s="14" t="n"/>
+      <c r="AB44" s="14" t="n">
+        <v>50</v>
+      </c>
       <c r="AC44" s="14" t="n"/>
       <c r="AD44" s="14" t="n"/>
-      <c r="AE44" s="15" t="n"/>
+      <c r="AE44" s="15" t="inlineStr">
+        <is>
+          <t>ดำเนินการ ตรวจประเมินภายใน/ภาย เป็นไปตามแผน (ถึง ต.ค.)</t>
+        </is>
+      </c>
       <c r="AF44" s="15" t="n"/>
       <c r="AG44" s="16" t="inlineStr">
         <is>
@@ -5493,12 +5599,14 @@
       <c r="AA45" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB45" s="14" t="n"/>
+      <c r="AB45" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC45" s="14" t="n"/>
       <c r="AD45" s="14" t="n"/>
       <c r="AE45" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ปรับปรุงฐานข้อมูลที่ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ปรับปรุงฐานข้อมูลที่ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF45" s="15" t="n"/>
@@ -5601,12 +5709,14 @@
       <c r="AA46" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB46" s="14" t="n"/>
+      <c r="AB46" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC46" s="14" t="n"/>
       <c r="AD46" s="14" t="n"/>
       <c r="AE46" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ใช้งานระบบ GRC เพื่อ เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ใช้งานระบบ GRC เพื่อ เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF46" s="15" t="n"/>
@@ -5709,12 +5819,14 @@
       <c r="AA47" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB47" s="14" t="n"/>
+      <c r="AB47" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC47" s="14" t="n"/>
       <c r="AD47" s="14" t="n"/>
       <c r="AE47" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ ทบทวนการทำ Value Cre เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ ทบทวนการทำ Value Cre เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF47" s="15" t="inlineStr">
@@ -5821,12 +5933,14 @@
       <c r="AA48" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB48" s="14" t="n"/>
+      <c r="AB48" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC48" s="14" t="n"/>
       <c r="AD48" s="14" t="n"/>
       <c r="AE48" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ กำหนดกระบวนการในการว เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ กำหนดกระบวนการในการว เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF48" s="15" t="n"/>
@@ -5929,12 +6043,14 @@
       <c r="AA49" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="AB49" s="14" t="n"/>
+      <c r="AB49" s="14" t="n">
+        <v>83.3</v>
+      </c>
       <c r="AC49" s="14" t="n"/>
       <c r="AD49" s="14" t="n"/>
       <c r="AE49" s="15" t="inlineStr">
         <is>
-          <t>ดำเนินการ พัฒนา Portfolio View เป็นไปตามแผน (ถึง ก.ย.)</t>
+          <t>ดำเนินการ พัฒนา Portfolio View เป็นไปตามแผน (ถึง ต.ค.)</t>
         </is>
       </c>
       <c r="AF49" s="15" t="n"/>
